--- a/available-bots.xlsx
+++ b/available-bots.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58840920-0442-4B80-994E-A652E236E095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB7631B-DA4C-4838-8639-27E5AA780505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{79371658-E0FE-43C3-8A19-9910316D4D47}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{79371658-E0FE-43C3-8A19-9910316D4D47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -421,9 +421,6 @@
     <t>机械公敌</t>
   </si>
   <si>
-    <t>水晶先锋</t>
-  </si>
-  <si>
     <t>大发明家</t>
   </si>
   <si>
@@ -1049,6 +1046,9 @@
   </si>
   <si>
     <t>Smolder</t>
+  </si>
+  <si>
+    <t>上古领主</t>
   </si>
 </sst>
 </file>
@@ -1116,9 +1116,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1156,7 +1156,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1262,7 +1262,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1404,7 +1404,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C1" t="s">
         <v>326</v>
-      </c>
-      <c r="C1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1621,7 +1621,7 @@
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1654,7 +1654,7 @@
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1742,7 +1742,7 @@
         <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -1830,7 +1830,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -1938,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C1" t="s">
         <v>326</v>
-      </c>
-      <c r="C1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1963,7 +1963,7 @@
         <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1985,7 +1985,7 @@
         <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1996,7 +1996,7 @@
         <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2007,7 +2007,7 @@
         <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2095,7 +2095,7 @@
         <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2216,7 +2216,7 @@
         <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2249,7 +2249,7 @@
         <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2260,7 +2260,7 @@
         <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -2271,7 +2271,7 @@
         <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2282,7 +2282,7 @@
         <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2293,7 +2293,7 @@
         <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2370,7 +2370,7 @@
         <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -2381,7 +2381,7 @@
         <v>119</v>
       </c>
       <c r="C41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -2392,7 +2392,7 @@
         <v>120</v>
       </c>
       <c r="C42" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -2414,7 +2414,7 @@
         <v>123</v>
       </c>
       <c r="C44" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -2425,7 +2425,7 @@
         <v>55</v>
       </c>
       <c r="C45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -2447,7 +2447,7 @@
         <v>125</v>
       </c>
       <c r="C47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -2458,7 +2458,7 @@
         <v>126</v>
       </c>
       <c r="C48" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -2477,10 +2477,10 @@
         <v>74</v>
       </c>
       <c r="B50" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -2510,10 +2510,10 @@
         <v>78</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C53" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -2532,10 +2532,10 @@
         <v>82</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -2543,10 +2543,10 @@
         <v>83</v>
       </c>
       <c r="B56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -2554,10 +2554,10 @@
         <v>84</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C57" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -2565,10 +2565,10 @@
         <v>85</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C58" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -2598,10 +2598,10 @@
         <v>90</v>
       </c>
       <c r="B61" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C61" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -2612,7 +2612,7 @@
         <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -2653,10 +2653,10 @@
         <v>103</v>
       </c>
       <c r="B66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C66" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -2675,10 +2675,10 @@
         <v>105</v>
       </c>
       <c r="B68" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C68" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -2686,10 +2686,10 @@
         <v>106</v>
       </c>
       <c r="B69" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C69" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -2697,10 +2697,10 @@
         <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C70" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -2708,10 +2708,10 @@
         <v>111</v>
       </c>
       <c r="B71" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C71" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -2719,10 +2719,10 @@
         <v>112</v>
       </c>
       <c r="B72" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C72" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -2730,10 +2730,10 @@
         <v>113</v>
       </c>
       <c r="B73" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -2752,10 +2752,10 @@
         <v>117</v>
       </c>
       <c r="B75" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C75" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -2763,10 +2763,10 @@
         <v>120</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -2774,10 +2774,10 @@
         <v>121</v>
       </c>
       <c r="B77" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C77" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -2796,10 +2796,10 @@
         <v>127</v>
       </c>
       <c r="B79" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C79" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -2807,10 +2807,10 @@
         <v>131</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C80" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -2829,10 +2829,10 @@
         <v>145</v>
       </c>
       <c r="B82" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C82" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -2840,10 +2840,10 @@
         <v>147</v>
       </c>
       <c r="B83" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C83" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -2851,10 +2851,10 @@
         <v>201</v>
       </c>
       <c r="B84" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C84" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -2873,10 +2873,10 @@
         <v>254</v>
       </c>
       <c r="B86" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C86" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -2884,10 +2884,10 @@
         <v>266</v>
       </c>
       <c r="B87" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C87" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -2895,10 +2895,10 @@
         <v>497</v>
       </c>
       <c r="B88" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C88" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -2906,10 +2906,10 @@
         <v>711</v>
       </c>
       <c r="B89" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C89" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
@@ -2917,10 +2917,10 @@
         <v>875</v>
       </c>
       <c r="B90" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C90" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -2928,10 +2928,10 @@
         <v>876</v>
       </c>
       <c r="B91" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C91" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -2939,10 +2939,10 @@
         <v>888</v>
       </c>
       <c r="B92" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C92" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
@@ -2950,10 +2950,10 @@
         <v>901</v>
       </c>
       <c r="B93" t="s">
+        <v>334</v>
+      </c>
+      <c r="C93" t="s">
         <v>335</v>
-      </c>
-      <c r="C93" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -2961,10 +2961,10 @@
         <v>902</v>
       </c>
       <c r="B94" t="s">
+        <v>321</v>
+      </c>
+      <c r="C94" t="s">
         <v>322</v>
-      </c>
-      <c r="C94" t="s">
-        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -2987,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C1" t="s">
         <v>326</v>
-      </c>
-      <c r="C1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -3012,7 +3012,7 @@
         <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3034,7 +3034,7 @@
         <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3045,7 +3045,7 @@
         <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -3056,7 +3056,7 @@
         <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3067,7 +3067,7 @@
         <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -3089,7 +3089,7 @@
         <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -3144,7 +3144,7 @@
         <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3177,7 +3177,7 @@
         <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -3331,7 +3331,7 @@
         <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3364,7 +3364,7 @@
         <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -3386,7 +3386,7 @@
         <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -3397,7 +3397,7 @@
         <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -3408,7 +3408,7 @@
         <v>111</v>
       </c>
       <c r="C39" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -3419,7 +3419,7 @@
         <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -3430,7 +3430,7 @@
         <v>113</v>
       </c>
       <c r="C41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -3441,7 +3441,7 @@
         <v>114</v>
       </c>
       <c r="C42" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -3452,7 +3452,7 @@
         <v>115</v>
       </c>
       <c r="C43" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -3463,7 +3463,7 @@
         <v>116</v>
       </c>
       <c r="C44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -3507,7 +3507,7 @@
         <v>117</v>
       </c>
       <c r="C48" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -3551,7 +3551,7 @@
         <v>118</v>
       </c>
       <c r="C52" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -3562,7 +3562,7 @@
         <v>119</v>
       </c>
       <c r="C53" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -3573,7 +3573,7 @@
         <v>120</v>
       </c>
       <c r="C54" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -3595,7 +3595,7 @@
         <v>121</v>
       </c>
       <c r="C56" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -3606,7 +3606,7 @@
         <v>122</v>
       </c>
       <c r="C57" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -3617,7 +3617,7 @@
         <v>123</v>
       </c>
       <c r="C58" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -3628,7 +3628,7 @@
         <v>55</v>
       </c>
       <c r="C59" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -3650,7 +3650,7 @@
         <v>124</v>
       </c>
       <c r="C61" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -3661,7 +3661,7 @@
         <v>125</v>
       </c>
       <c r="C62" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -3672,7 +3672,7 @@
         <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -3691,10 +3691,10 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>127</v>
+        <v>336</v>
       </c>
       <c r="C65" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -3702,10 +3702,10 @@
         <v>74</v>
       </c>
       <c r="B66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C66" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -3746,10 +3746,10 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C70" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -3757,10 +3757,10 @@
         <v>79</v>
       </c>
       <c r="B71" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C71" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -3768,10 +3768,10 @@
         <v>80</v>
       </c>
       <c r="B72" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C72" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -3790,10 +3790,10 @@
         <v>82</v>
       </c>
       <c r="B74" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C74" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -3801,10 +3801,10 @@
         <v>83</v>
       </c>
       <c r="B75" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C75" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -3812,10 +3812,10 @@
         <v>84</v>
       </c>
       <c r="B76" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C76" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -3823,10 +3823,10 @@
         <v>85</v>
       </c>
       <c r="B77" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C77" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -3856,10 +3856,10 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C80" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -3867,10 +3867,10 @@
         <v>91</v>
       </c>
       <c r="B81" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C81" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -3878,10 +3878,10 @@
         <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C82" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -3892,7 +3892,7 @@
         <v>72</v>
       </c>
       <c r="C83" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -3922,10 +3922,10 @@
         <v>101</v>
       </c>
       <c r="B86" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C86" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -3944,10 +3944,10 @@
         <v>103</v>
       </c>
       <c r="B88" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C88" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -3966,10 +3966,10 @@
         <v>105</v>
       </c>
       <c r="B90" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C90" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -3977,10 +3977,10 @@
         <v>106</v>
       </c>
       <c r="B91" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C91" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -3988,10 +3988,10 @@
         <v>107</v>
       </c>
       <c r="B92" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C92" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
@@ -3999,10 +3999,10 @@
         <v>110</v>
       </c>
       <c r="B93" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C93" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -4010,10 +4010,10 @@
         <v>111</v>
       </c>
       <c r="B94" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C94" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
@@ -4021,10 +4021,10 @@
         <v>112</v>
       </c>
       <c r="B95" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
@@ -4032,10 +4032,10 @@
         <v>113</v>
       </c>
       <c r="B96" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
@@ -4043,10 +4043,10 @@
         <v>114</v>
       </c>
       <c r="B97" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C97" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -4065,10 +4065,10 @@
         <v>117</v>
       </c>
       <c r="B99" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C99" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
@@ -4076,10 +4076,10 @@
         <v>119</v>
       </c>
       <c r="B100" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C100" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
@@ -4087,10 +4087,10 @@
         <v>120</v>
       </c>
       <c r="B101" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C101" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
@@ -4098,10 +4098,10 @@
         <v>121</v>
       </c>
       <c r="B102" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C102" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -4120,10 +4120,10 @@
         <v>126</v>
       </c>
       <c r="B104" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C104" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
@@ -4131,10 +4131,10 @@
         <v>127</v>
       </c>
       <c r="B105" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C105" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
@@ -4142,10 +4142,10 @@
         <v>131</v>
       </c>
       <c r="B106" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C106" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
@@ -4153,10 +4153,10 @@
         <v>133</v>
       </c>
       <c r="B107" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C107" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
@@ -4164,10 +4164,10 @@
         <v>134</v>
       </c>
       <c r="B108" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C108" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
@@ -4175,10 +4175,10 @@
         <v>136</v>
       </c>
       <c r="B109" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C109" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -4186,10 +4186,10 @@
         <v>141</v>
       </c>
       <c r="B110" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C110" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
@@ -4197,10 +4197,10 @@
         <v>142</v>
       </c>
       <c r="B111" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
@@ -4219,10 +4219,10 @@
         <v>145</v>
       </c>
       <c r="B113" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C113" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
@@ -4230,10 +4230,10 @@
         <v>147</v>
       </c>
       <c r="B114" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C114" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
@@ -4241,10 +4241,10 @@
         <v>150</v>
       </c>
       <c r="B115" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C115" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
@@ -4252,10 +4252,10 @@
         <v>154</v>
       </c>
       <c r="B116" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C116" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
@@ -4263,10 +4263,10 @@
         <v>157</v>
       </c>
       <c r="B117" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C117" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
@@ -4274,10 +4274,10 @@
         <v>161</v>
       </c>
       <c r="B118" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C118" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
@@ -4285,10 +4285,10 @@
         <v>163</v>
       </c>
       <c r="B119" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C119" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
@@ -4296,10 +4296,10 @@
         <v>164</v>
       </c>
       <c r="B120" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C120" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -4307,10 +4307,10 @@
         <v>166</v>
       </c>
       <c r="B121" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C121" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
@@ -4318,10 +4318,10 @@
         <v>200</v>
       </c>
       <c r="B122" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C122" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
@@ -4329,10 +4329,10 @@
         <v>201</v>
       </c>
       <c r="B123" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C123" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
@@ -4340,10 +4340,10 @@
         <v>202</v>
       </c>
       <c r="B124" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C124" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
@@ -4351,10 +4351,10 @@
         <v>203</v>
       </c>
       <c r="B125" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C125" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
@@ -4362,10 +4362,10 @@
         <v>221</v>
       </c>
       <c r="B126" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C126" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
@@ -4373,10 +4373,10 @@
         <v>222</v>
       </c>
       <c r="B127" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C127" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
@@ -4384,10 +4384,10 @@
         <v>223</v>
       </c>
       <c r="B128" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C128" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
@@ -4395,10 +4395,10 @@
         <v>233</v>
       </c>
       <c r="B129" t="s">
+        <v>327</v>
+      </c>
+      <c r="C129" t="s">
         <v>328</v>
-      </c>
-      <c r="C129" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
@@ -4406,10 +4406,10 @@
         <v>234</v>
       </c>
       <c r="B130" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C130" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
@@ -4417,10 +4417,10 @@
         <v>235</v>
       </c>
       <c r="B131" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C131" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -4439,10 +4439,10 @@
         <v>238</v>
       </c>
       <c r="B133" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C133" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
@@ -4450,10 +4450,10 @@
         <v>240</v>
       </c>
       <c r="B134" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C134" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
@@ -4461,10 +4461,10 @@
         <v>245</v>
       </c>
       <c r="B135" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C135" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
@@ -4472,10 +4472,10 @@
         <v>246</v>
       </c>
       <c r="B136" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C136" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
@@ -4483,10 +4483,10 @@
         <v>254</v>
       </c>
       <c r="B137" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C137" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
@@ -4494,10 +4494,10 @@
         <v>266</v>
       </c>
       <c r="B138" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C138" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
@@ -4505,10 +4505,10 @@
         <v>267</v>
       </c>
       <c r="B139" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C139" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
@@ -4516,10 +4516,10 @@
         <v>268</v>
       </c>
       <c r="B140" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C140" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
@@ -4527,10 +4527,10 @@
         <v>350</v>
       </c>
       <c r="B141" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C141" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
@@ -4538,10 +4538,10 @@
         <v>360</v>
       </c>
       <c r="B142" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C142" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -4549,10 +4549,10 @@
         <v>412</v>
       </c>
       <c r="B143" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C143" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
@@ -4560,10 +4560,10 @@
         <v>420</v>
       </c>
       <c r="B144" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C144" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
@@ -4571,10 +4571,10 @@
         <v>421</v>
       </c>
       <c r="B145" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C145" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
@@ -4582,10 +4582,10 @@
         <v>427</v>
       </c>
       <c r="B146" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C146" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
@@ -4593,10 +4593,10 @@
         <v>429</v>
       </c>
       <c r="B147" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C147" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
@@ -4604,10 +4604,10 @@
         <v>432</v>
       </c>
       <c r="B148" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C148" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
@@ -4615,10 +4615,10 @@
         <v>497</v>
       </c>
       <c r="B149" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C149" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
@@ -4626,10 +4626,10 @@
         <v>498</v>
       </c>
       <c r="B150" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C150" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
@@ -4637,10 +4637,10 @@
         <v>516</v>
       </c>
       <c r="B151" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C151" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
@@ -4648,10 +4648,10 @@
         <v>517</v>
       </c>
       <c r="B152" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C152" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -4659,10 +4659,10 @@
         <v>518</v>
       </c>
       <c r="B153" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C153" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -4670,10 +4670,10 @@
         <v>523</v>
       </c>
       <c r="B154" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C154" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -4681,10 +4681,10 @@
         <v>526</v>
       </c>
       <c r="B155" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C155" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -4692,10 +4692,10 @@
         <v>555</v>
       </c>
       <c r="B156" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C156" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
@@ -4703,10 +4703,10 @@
         <v>711</v>
       </c>
       <c r="B157" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C157" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
@@ -4714,10 +4714,10 @@
         <v>777</v>
       </c>
       <c r="B158" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C158" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
@@ -4725,10 +4725,10 @@
         <v>875</v>
       </c>
       <c r="B159" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C159" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
@@ -4736,10 +4736,10 @@
         <v>876</v>
       </c>
       <c r="B160" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C160" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
@@ -4747,10 +4747,10 @@
         <v>887</v>
       </c>
       <c r="B161" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C161" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
@@ -4758,10 +4758,10 @@
         <v>888</v>
       </c>
       <c r="B162" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C162" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
@@ -4769,10 +4769,10 @@
         <v>895</v>
       </c>
       <c r="B163" t="s">
+        <v>318</v>
+      </c>
+      <c r="C163" t="s">
         <v>319</v>
-      </c>
-      <c r="C163" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
@@ -4780,10 +4780,10 @@
         <v>897</v>
       </c>
       <c r="B164" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C164" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -4791,10 +4791,10 @@
         <v>901</v>
       </c>
       <c r="B165" t="s">
+        <v>334</v>
+      </c>
+      <c r="C165" t="s">
         <v>335</v>
-      </c>
-      <c r="C165" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
@@ -4802,10 +4802,10 @@
         <v>902</v>
       </c>
       <c r="B166" t="s">
+        <v>321</v>
+      </c>
+      <c r="C166" t="s">
         <v>322</v>
-      </c>
-      <c r="C166" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
@@ -4813,10 +4813,10 @@
         <v>910</v>
       </c>
       <c r="B167" t="s">
+        <v>329</v>
+      </c>
+      <c r="C167" t="s">
         <v>330</v>
-      </c>
-      <c r="C167" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
@@ -4824,10 +4824,10 @@
         <v>950</v>
       </c>
       <c r="B168" t="s">
+        <v>323</v>
+      </c>
+      <c r="C168" t="s">
         <v>324</v>
-      </c>
-      <c r="C168" t="s">
-        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/available-bots.xlsx
+++ b/available-bots.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB7631B-DA4C-4838-8639-27E5AA780505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58F8E0D-509B-4BEF-9077-E9319D8BD690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{79371658-E0FE-43C3-8A19-9910316D4D47}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{79371658-E0FE-43C3-8A19-9910316D4D47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="337">
   <si>
     <t>championId</t>
   </si>
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF61A57-5822-4115-87D6-6E94EB78B234}">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1450,57 +1450,57 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1571,189 +1571,189 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>215</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
         <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
+        <v>54</v>
+      </c>
+      <c r="B26" t="s">
         <v>51</v>
       </c>
-      <c r="B26" t="s">
-        <v>47</v>
-      </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s">
-        <v>315</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1780,13 +1780,13 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="C34" t="s">
-        <v>63</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1802,123 +1802,387 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>71</v>
+        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>241</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C43" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>86</v>
+        <v>248</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46">
+        <v>106</v>
+      </c>
+      <c r="B46" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>110</v>
+      </c>
+      <c r="B47" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>111</v>
+      </c>
+      <c r="B48" t="s">
+        <v>144</v>
+      </c>
+      <c r="C48" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>112</v>
+      </c>
+      <c r="B49" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>113</v>
+      </c>
+      <c r="B50" t="s">
+        <v>146</v>
+      </c>
+      <c r="C50" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>115</v>
+      </c>
+      <c r="B51" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>117</v>
+      </c>
+      <c r="B52" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>120</v>
+      </c>
+      <c r="B53" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>121</v>
+      </c>
+      <c r="B54" t="s">
+        <v>151</v>
+      </c>
+      <c r="C54" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>122</v>
+      </c>
+      <c r="B55" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>127</v>
+      </c>
+      <c r="B56" t="s">
+        <v>153</v>
+      </c>
+      <c r="C56" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>131</v>
+      </c>
+      <c r="B57" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>143</v>
+      </c>
+      <c r="B58" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>145</v>
+      </c>
+      <c r="B59" t="s">
+        <v>160</v>
+      </c>
+      <c r="C59" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>147</v>
+      </c>
+      <c r="B60" t="s">
+        <v>161</v>
+      </c>
+      <c r="C60" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>201</v>
+      </c>
+      <c r="B61" t="s">
+        <v>169</v>
+      </c>
+      <c r="C61" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62">
         <v>236</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B62" t="s">
         <v>87</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C62" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>254</v>
+      </c>
+      <c r="B63" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>497</v>
+      </c>
+      <c r="B64" t="s">
+        <v>193</v>
+      </c>
+      <c r="C64" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>711</v>
+      </c>
+      <c r="B65" t="s">
+        <v>201</v>
+      </c>
+      <c r="C65" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>875</v>
+      </c>
+      <c r="B66" t="s">
+        <v>203</v>
+      </c>
+      <c r="C66" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>876</v>
+      </c>
+      <c r="B67" t="s">
+        <v>204</v>
+      </c>
+      <c r="C67" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>888</v>
+      </c>
+      <c r="B68" t="s">
+        <v>206</v>
+      </c>
+      <c r="C68" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>901</v>
+      </c>
+      <c r="B69" t="s">
+        <v>334</v>
+      </c>
+      <c r="C69" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>902</v>
+      </c>
+      <c r="B70" t="s">
+        <v>321</v>
+      </c>
+      <c r="C70" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -1930,7 +2194,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C1DA04B-86DE-4C1C-948C-D98ADF48BF05}">
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1957,1013 +2221,936 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>207</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
         <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
         <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
         <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>212</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>213</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>213</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>218</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>113</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>219</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
+        <v>54</v>
+      </c>
+      <c r="B37" t="s">
         <v>51</v>
       </c>
-      <c r="B37" t="s">
-        <v>47</v>
-      </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s">
-        <v>50</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>52</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>225</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42">
+        <v>63</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" t="s">
         <v>57</v>
-      </c>
-      <c r="B42" t="s">
-        <v>120</v>
-      </c>
-      <c r="C42" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>125</v>
       </c>
       <c r="C43" t="s">
-        <v>54</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C44" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>315</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C46" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>231</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C48" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B49" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C49" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C50" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="C51" t="s">
-        <v>61</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>63</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C53" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>238</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B56" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="C57" t="s">
-        <v>240</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="C58" t="s">
-        <v>241</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B60" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="C60" t="s">
-        <v>71</v>
+        <v>247</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>242</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="C62" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="C63" t="s">
-        <v>74</v>
+        <v>249</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="C64" t="s">
-        <v>76</v>
+        <v>251</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B65" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>252</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="B66" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C66" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="C67" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B68" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="C68" t="s">
-        <v>248</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B69" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C69" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B70" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C70" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B71" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C71" t="s">
-        <v>252</v>
+        <v>316</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B72" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C72" t="s">
-        <v>253</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="B74" t="s">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="C74" t="s">
-        <v>82</v>
+        <v>261</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="B75" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="C75" t="s">
-        <v>256</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="B76" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C76" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="B77" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C77" t="s">
-        <v>316</v>
+        <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>122</v>
+        <v>201</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>275</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>127</v>
+        <v>236</v>
       </c>
       <c r="B79" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s">
-        <v>260</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>131</v>
+        <v>254</v>
       </c>
       <c r="B80" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="C80" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>143</v>
+        <v>497</v>
       </c>
       <c r="B81" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>299</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>145</v>
+        <v>711</v>
       </c>
       <c r="B82" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="C82" t="s">
-        <v>267</v>
+        <v>307</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>147</v>
+        <v>875</v>
       </c>
       <c r="B83" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>201</v>
+        <v>876</v>
       </c>
       <c r="B84" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="C84" t="s">
-        <v>275</v>
+        <v>310</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>236</v>
+        <v>888</v>
       </c>
       <c r="B85" t="s">
-        <v>87</v>
+        <v>206</v>
       </c>
       <c r="C85" t="s">
-        <v>88</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86">
-        <v>254</v>
+        <v>901</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>334</v>
       </c>
       <c r="C86" t="s">
-        <v>287</v>
+        <v>335</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87">
-        <v>266</v>
+        <v>902</v>
       </c>
       <c r="B87" t="s">
-        <v>182</v>
+        <v>321</v>
       </c>
       <c r="C87" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88">
-        <v>497</v>
-      </c>
-      <c r="B88" t="s">
-        <v>193</v>
-      </c>
-      <c r="C88" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89">
-        <v>711</v>
-      </c>
-      <c r="B89" t="s">
-        <v>201</v>
-      </c>
-      <c r="C89" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90">
-        <v>875</v>
-      </c>
-      <c r="B90" t="s">
-        <v>203</v>
-      </c>
-      <c r="C90" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91">
-        <v>876</v>
-      </c>
-      <c r="B91" t="s">
-        <v>204</v>
-      </c>
-      <c r="C91" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A92">
-        <v>888</v>
-      </c>
-      <c r="B92" t="s">
-        <v>206</v>
-      </c>
-      <c r="C92" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A93">
-        <v>901</v>
-      </c>
-      <c r="B93" t="s">
-        <v>334</v>
-      </c>
-      <c r="C93" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A94">
-        <v>902</v>
-      </c>
-      <c r="B94" t="s">
-        <v>321</v>
-      </c>
-      <c r="C94" t="s">
         <v>322</v>
       </c>
     </row>

--- a/available-bots.xlsx
+++ b/available-bots.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58F8E0D-509B-4BEF-9077-E9319D8BD690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D89064-AAB3-4FFB-AFD4-B75EE84F4644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{79371658-E0FE-43C3-8A19-9910316D4D47}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="367">
   <si>
     <t>championId</t>
   </si>
@@ -313,9 +313,6 @@
     <t>雪原双子</t>
   </si>
   <si>
-    <t>Nunu &amp; Willump</t>
-  </si>
-  <si>
     <t>蛮族之王</t>
   </si>
   <si>
@@ -721,18 +718,12 @@
     <t>Maokai</t>
   </si>
   <si>
-    <t>Jarvan IV</t>
-  </si>
-  <si>
     <t>Elise</t>
   </si>
   <si>
     <t>Orianna</t>
   </si>
   <si>
-    <t>Lee Sin</t>
-  </si>
-  <si>
     <t>Vayne</t>
   </si>
   <si>
@@ -832,9 +823,6 @@
     <t>Syndra</t>
   </si>
   <si>
-    <t>Aurelion Sol</t>
-  </si>
-  <si>
     <t>Kayn</t>
   </si>
   <si>
@@ -880,9 +868,6 @@
     <t>Jinx</t>
   </si>
   <si>
-    <t>Tahm Kench</t>
-  </si>
-  <si>
     <t>Viego</t>
   </si>
   <si>
@@ -925,9 +910,6 @@
     <t>Illaoi</t>
   </si>
   <si>
-    <t>Rek'Sai</t>
-  </si>
-  <si>
     <t>Ivern</t>
   </si>
   <si>
@@ -1033,15 +1015,6 @@
     <t>Hwei</t>
   </si>
   <si>
-    <t>Vel'Koz</t>
-  </si>
-  <si>
-    <t>Bel'Veth</t>
-  </si>
-  <si>
-    <t>K'Sante</t>
-  </si>
-  <si>
     <t>炽炎雏龙</t>
   </si>
   <si>
@@ -1049,6 +1022,123 @@
   </si>
   <si>
     <t>上古领主</t>
+  </si>
+  <si>
+    <t>TwistedFate</t>
+  </si>
+  <si>
+    <t>XinZhao</t>
+  </si>
+  <si>
+    <t>MasterYi</t>
+  </si>
+  <si>
+    <t>Nunu</t>
+  </si>
+  <si>
+    <t>MissFortune</t>
+  </si>
+  <si>
+    <t>Chogath</t>
+  </si>
+  <si>
+    <t>DrMundo</t>
+  </si>
+  <si>
+    <t>JarvanIV</t>
+  </si>
+  <si>
+    <t>MonkeyKing</t>
+  </si>
+  <si>
+    <t>LeeSin</t>
+  </si>
+  <si>
+    <t>KogMaw</t>
+  </si>
+  <si>
+    <t>AurelionSol</t>
+  </si>
+  <si>
+    <t>Kaisa</t>
+  </si>
+  <si>
+    <t>Velkoz</t>
+  </si>
+  <si>
+    <t>Belveth</t>
+  </si>
+  <si>
+    <t>TahmKench</t>
+  </si>
+  <si>
+    <t>RekSai</t>
+  </si>
+  <si>
+    <t>Renata</t>
+  </si>
+  <si>
+    <t>双界灵兔</t>
+  </si>
+  <si>
+    <t>Aurora</t>
+  </si>
+  <si>
+    <t>KSante</t>
+  </si>
+  <si>
+    <t>锐雯</t>
+  </si>
+  <si>
+    <t>Strawberry_Riven</t>
+  </si>
+  <si>
+    <t>金克丝</t>
+  </si>
+  <si>
+    <t>Strawberry_Jinx</t>
+  </si>
+  <si>
+    <t>蕾欧娜</t>
+  </si>
+  <si>
+    <t>Strawberry_Leona</t>
+  </si>
+  <si>
+    <t>萨勒芬妮</t>
+  </si>
+  <si>
+    <t>Strawberry_Seraphine</t>
+  </si>
+  <si>
+    <t>贝蕾亚</t>
+  </si>
+  <si>
+    <t>Strawberry_Briar</t>
+  </si>
+  <si>
+    <t>亚索</t>
+  </si>
+  <si>
+    <t>Strawberry_Yasuo</t>
+  </si>
+  <si>
+    <t>阿萝拉</t>
+  </si>
+  <si>
+    <t>Strawberry_Aurora</t>
+  </si>
+  <si>
+    <t>俄洛伊</t>
+  </si>
+  <si>
+    <t>Strawberry_Illaoi</t>
+  </si>
+  <si>
+    <t>霞</t>
+  </si>
+  <si>
+    <t>Strawberry_Xayah</t>
   </si>
 </sst>
 </file>
@@ -1420,10 +1510,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1453,10 +1543,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1464,10 +1554,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1475,10 +1565,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1574,10 +1664,10 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
         <v>92</v>
-      </c>
-      <c r="C15" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1585,10 +1675,10 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" t="s">
         <v>97</v>
-      </c>
-      <c r="C16" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1599,7 +1689,7 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1618,10 +1708,10 @@
         <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1629,10 +1719,10 @@
         <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1640,10 +1730,10 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1706,10 +1796,10 @@
         <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1717,10 +1807,10 @@
         <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1731,7 +1821,7 @@
         <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1739,10 +1829,10 @@
         <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -1750,10 +1840,10 @@
         <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C31" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1783,10 +1873,10 @@
         <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1805,10 +1895,10 @@
         <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -1816,10 +1906,10 @@
         <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -1827,10 +1917,10 @@
         <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -1838,10 +1928,10 @@
         <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -1893,10 +1983,10 @@
         <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -1904,10 +1994,10 @@
         <v>105</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C45" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -1915,10 +2005,10 @@
         <v>106</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C46" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -1926,10 +2016,10 @@
         <v>110</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C47" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -1937,10 +2027,10 @@
         <v>111</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C48" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -1948,10 +2038,10 @@
         <v>112</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -1959,10 +2049,10 @@
         <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -1981,10 +2071,10 @@
         <v>117</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C52" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -1992,10 +2082,10 @@
         <v>120</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C53" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -2003,10 +2093,10 @@
         <v>121</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C54" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -2025,10 +2115,10 @@
         <v>127</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C56" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -2036,10 +2126,10 @@
         <v>131</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -2058,10 +2148,10 @@
         <v>145</v>
       </c>
       <c r="B59" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C59" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -2069,10 +2159,10 @@
         <v>147</v>
       </c>
       <c r="B60" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C60" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -2080,10 +2170,10 @@
         <v>201</v>
       </c>
       <c r="B61" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C61" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -2102,10 +2192,10 @@
         <v>254</v>
       </c>
       <c r="B63" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C63" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -2113,10 +2203,10 @@
         <v>497</v>
       </c>
       <c r="B64" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -2124,10 +2214,10 @@
         <v>711</v>
       </c>
       <c r="B65" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C65" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -2135,10 +2225,10 @@
         <v>875</v>
       </c>
       <c r="B66" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C66" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -2146,10 +2236,10 @@
         <v>876</v>
       </c>
       <c r="B67" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C67" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -2157,10 +2247,10 @@
         <v>888</v>
       </c>
       <c r="B68" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C68" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -2168,10 +2258,10 @@
         <v>901</v>
       </c>
       <c r="B69" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C69" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -2179,10 +2269,10 @@
         <v>902</v>
       </c>
       <c r="B70" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C70" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -2202,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -2235,10 +2325,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -2246,10 +2336,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -2257,10 +2347,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -2389,10 +2479,10 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" t="s">
         <v>92</v>
-      </c>
-      <c r="C18" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -2433,10 +2523,10 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" t="s">
         <v>97</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2458,7 +2548,7 @@
         <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2491,7 +2581,7 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2499,10 +2589,10 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2510,10 +2600,10 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2521,10 +2611,10 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -2532,10 +2622,10 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2609,10 +2699,10 @@
         <v>56</v>
       </c>
       <c r="B38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -2620,10 +2710,10 @@
         <v>57</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -2645,7 +2735,7 @@
         <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -2664,10 +2754,10 @@
         <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -2675,10 +2765,10 @@
         <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C44" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -2719,10 +2809,10 @@
         <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C48" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -2741,10 +2831,10 @@
         <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -2752,10 +2842,10 @@
         <v>83</v>
       </c>
       <c r="B51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C51" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -2763,10 +2853,10 @@
         <v>84</v>
       </c>
       <c r="B52" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C52" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -2774,10 +2864,10 @@
         <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C53" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -2810,7 +2900,7 @@
         <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -2851,10 +2941,10 @@
         <v>103</v>
       </c>
       <c r="B60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C60" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -2873,10 +2963,10 @@
         <v>105</v>
       </c>
       <c r="B62" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C62" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -2884,10 +2974,10 @@
         <v>106</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C63" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -2895,10 +2985,10 @@
         <v>110</v>
       </c>
       <c r="B64" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C64" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -2906,10 +2996,10 @@
         <v>111</v>
       </c>
       <c r="B65" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C65" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -2917,10 +3007,10 @@
         <v>112</v>
       </c>
       <c r="B66" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C66" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -2928,10 +3018,10 @@
         <v>113</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C67" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -2950,10 +3040,10 @@
         <v>117</v>
       </c>
       <c r="B69" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C69" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -2961,10 +3051,10 @@
         <v>120</v>
       </c>
       <c r="B70" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C70" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -2972,10 +3062,10 @@
         <v>121</v>
       </c>
       <c r="B71" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C71" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -2994,10 +3084,10 @@
         <v>127</v>
       </c>
       <c r="B73" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C73" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -3005,10 +3095,10 @@
         <v>131</v>
       </c>
       <c r="B74" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -3027,10 +3117,10 @@
         <v>145</v>
       </c>
       <c r="B76" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C76" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -3038,10 +3128,10 @@
         <v>147</v>
       </c>
       <c r="B77" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C77" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -3049,10 +3139,10 @@
         <v>201</v>
       </c>
       <c r="B78" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C78" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -3071,10 +3161,10 @@
         <v>254</v>
       </c>
       <c r="B80" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C80" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -3082,10 +3172,10 @@
         <v>497</v>
       </c>
       <c r="B81" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -3093,10 +3183,10 @@
         <v>711</v>
       </c>
       <c r="B82" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C82" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -3104,10 +3194,10 @@
         <v>875</v>
       </c>
       <c r="B83" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C83" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -3115,10 +3205,10 @@
         <v>876</v>
       </c>
       <c r="B84" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C84" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -3126,10 +3216,10 @@
         <v>888</v>
       </c>
       <c r="B85" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C85" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -3137,10 +3227,10 @@
         <v>901</v>
       </c>
       <c r="B86" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C86" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -3148,10 +3238,10 @@
         <v>902</v>
       </c>
       <c r="B87" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C87" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3256,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A1820C-C33D-44E8-9D81-D0A634174CBA}">
-  <dimension ref="A1:C168"/>
+  <dimension ref="A1:C178"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -3174,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -3196,10 +3286,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3218,10 +3308,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>208</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3229,10 +3319,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -3240,10 +3330,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3251,10 +3341,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -3276,7 +3366,7 @@
         <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -3298,7 +3388,7 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3328,10 +3418,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3361,10 +3451,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -3397,7 +3487,7 @@
         <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3408,7 +3498,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>332</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3427,10 +3517,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
         <v>92</v>
-      </c>
-      <c r="C24" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3471,10 +3561,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
         <v>94</v>
-      </c>
-      <c r="C28" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3482,10 +3572,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3493,10 +3583,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" t="s">
         <v>97</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -3518,7 +3608,7 @@
         <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>213</v>
+        <v>333</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3548,10 +3638,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -3559,10 +3649,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" t="s">
         <v>101</v>
-      </c>
-      <c r="C36" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -3573,7 +3663,7 @@
         <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>215</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -3581,10 +3671,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -3592,10 +3682,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -3603,10 +3693,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -3614,10 +3704,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -3625,10 +3715,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C42" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -3636,10 +3726,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -3647,10 +3737,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -3691,10 +3781,10 @@
         <v>50</v>
       </c>
       <c r="B48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -3735,10 +3825,10 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C52" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -3746,10 +3836,10 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C53" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -3757,10 +3847,10 @@
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C54" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -3779,10 +3869,10 @@
         <v>59</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C56" t="s">
-        <v>227</v>
+        <v>335</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -3790,10 +3880,10 @@
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -3801,10 +3891,10 @@
         <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C58" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -3815,7 +3905,7 @@
         <v>55</v>
       </c>
       <c r="C59" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -3834,10 +3924,10 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C61" t="s">
-        <v>230</v>
+        <v>337</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -3845,10 +3935,10 @@
         <v>67</v>
       </c>
       <c r="B62" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C62" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -3856,10 +3946,10 @@
         <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C63" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -3878,10 +3968,10 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C65" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -3889,10 +3979,10 @@
         <v>74</v>
       </c>
       <c r="B66" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C66" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -3933,10 +4023,10 @@
         <v>78</v>
       </c>
       <c r="B70" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C70" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -3944,10 +4034,10 @@
         <v>79</v>
       </c>
       <c r="B71" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C71" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -3955,10 +4045,10 @@
         <v>80</v>
       </c>
       <c r="B72" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C72" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -3977,10 +4067,10 @@
         <v>82</v>
       </c>
       <c r="B74" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C74" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -3988,10 +4078,10 @@
         <v>83</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C75" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -3999,10 +4089,10 @@
         <v>84</v>
       </c>
       <c r="B76" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C76" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -4010,10 +4100,10 @@
         <v>85</v>
       </c>
       <c r="B77" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C77" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -4043,10 +4133,10 @@
         <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C80" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -4054,10 +4144,10 @@
         <v>91</v>
       </c>
       <c r="B81" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C81" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -4065,10 +4155,10 @@
         <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C82" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -4079,7 +4169,7 @@
         <v>72</v>
       </c>
       <c r="C83" t="s">
-        <v>245</v>
+        <v>338</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -4109,10 +4199,10 @@
         <v>101</v>
       </c>
       <c r="B86" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C86" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -4131,10 +4221,10 @@
         <v>103</v>
       </c>
       <c r="B88" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C88" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -4153,10 +4243,10 @@
         <v>105</v>
       </c>
       <c r="B90" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C90" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -4164,10 +4254,10 @@
         <v>106</v>
       </c>
       <c r="B91" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C91" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -4175,10 +4265,10 @@
         <v>107</v>
       </c>
       <c r="B92" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C92" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
@@ -4186,10 +4276,10 @@
         <v>110</v>
       </c>
       <c r="B93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C93" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -4197,10 +4287,10 @@
         <v>111</v>
       </c>
       <c r="B94" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C94" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
@@ -4208,10 +4298,10 @@
         <v>112</v>
       </c>
       <c r="B95" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C95" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
@@ -4219,10 +4309,10 @@
         <v>113</v>
       </c>
       <c r="B96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C96" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
@@ -4230,10 +4320,10 @@
         <v>114</v>
       </c>
       <c r="B97" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -4252,10 +4342,10 @@
         <v>117</v>
       </c>
       <c r="B99" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C99" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
@@ -4263,10 +4353,10 @@
         <v>119</v>
       </c>
       <c r="B100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C100" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
@@ -4274,10 +4364,10 @@
         <v>120</v>
       </c>
       <c r="B101" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C101" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
@@ -4285,10 +4375,10 @@
         <v>121</v>
       </c>
       <c r="B102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C102" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -4307,10 +4397,10 @@
         <v>126</v>
       </c>
       <c r="B104" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C104" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
@@ -4318,10 +4408,10 @@
         <v>127</v>
       </c>
       <c r="B105" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C105" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
@@ -4329,10 +4419,10 @@
         <v>131</v>
       </c>
       <c r="B106" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C106" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
@@ -4340,10 +4430,10 @@
         <v>133</v>
       </c>
       <c r="B107" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C107" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
@@ -4351,10 +4441,10 @@
         <v>134</v>
       </c>
       <c r="B108" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C108" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
@@ -4362,10 +4452,10 @@
         <v>136</v>
       </c>
       <c r="B109" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C109" t="s">
-        <v>264</v>
+        <v>339</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -4373,10 +4463,10 @@
         <v>141</v>
       </c>
       <c r="B110" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C110" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
@@ -4384,10 +4474,10 @@
         <v>142</v>
       </c>
       <c r="B111" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C111" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
@@ -4406,10 +4496,10 @@
         <v>145</v>
       </c>
       <c r="B113" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C113" t="s">
-        <v>267</v>
+        <v>340</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
@@ -4417,10 +4507,10 @@
         <v>147</v>
       </c>
       <c r="B114" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C114" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
@@ -4428,10 +4518,10 @@
         <v>150</v>
       </c>
       <c r="B115" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C115" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
@@ -4439,10 +4529,10 @@
         <v>154</v>
       </c>
       <c r="B116" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C116" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
@@ -4450,10 +4540,10 @@
         <v>157</v>
       </c>
       <c r="B117" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C117" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
@@ -4461,10 +4551,10 @@
         <v>161</v>
       </c>
       <c r="B118" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C118" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
@@ -4472,10 +4562,10 @@
         <v>163</v>
       </c>
       <c r="B119" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C119" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
@@ -4483,10 +4573,10 @@
         <v>164</v>
       </c>
       <c r="B120" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C120" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -4494,10 +4584,10 @@
         <v>166</v>
       </c>
       <c r="B121" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C121" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
@@ -4505,10 +4595,10 @@
         <v>200</v>
       </c>
       <c r="B122" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C122" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
@@ -4516,10 +4606,10 @@
         <v>201</v>
       </c>
       <c r="B123" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C123" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
@@ -4527,10 +4617,10 @@
         <v>202</v>
       </c>
       <c r="B124" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C124" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
@@ -4538,10 +4628,10 @@
         <v>203</v>
       </c>
       <c r="B125" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C125" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
@@ -4549,10 +4639,10 @@
         <v>221</v>
       </c>
       <c r="B126" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C126" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
@@ -4560,10 +4650,10 @@
         <v>222</v>
       </c>
       <c r="B127" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C127" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
@@ -4571,10 +4661,10 @@
         <v>223</v>
       </c>
       <c r="B128" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C128" t="s">
-        <v>280</v>
+        <v>343</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
@@ -4582,10 +4672,10 @@
         <v>233</v>
       </c>
       <c r="B129" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C129" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
@@ -4593,10 +4683,10 @@
         <v>234</v>
       </c>
       <c r="B130" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C130" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
@@ -4604,10 +4694,10 @@
         <v>235</v>
       </c>
       <c r="B131" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C131" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -4626,10 +4716,10 @@
         <v>238</v>
       </c>
       <c r="B133" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C133" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
@@ -4637,10 +4727,10 @@
         <v>240</v>
       </c>
       <c r="B134" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C134" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
@@ -4648,10 +4738,10 @@
         <v>245</v>
       </c>
       <c r="B135" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C135" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
@@ -4659,10 +4749,10 @@
         <v>246</v>
       </c>
       <c r="B136" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C136" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
@@ -4670,10 +4760,10 @@
         <v>254</v>
       </c>
       <c r="B137" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C137" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
@@ -4681,10 +4771,10 @@
         <v>266</v>
       </c>
       <c r="B138" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C138" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
@@ -4692,10 +4782,10 @@
         <v>267</v>
       </c>
       <c r="B139" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C139" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
@@ -4703,10 +4793,10 @@
         <v>268</v>
       </c>
       <c r="B140" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C140" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
@@ -4714,10 +4804,10 @@
         <v>350</v>
       </c>
       <c r="B141" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C141" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
@@ -4725,10 +4815,10 @@
         <v>360</v>
       </c>
       <c r="B142" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C142" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -4736,10 +4826,10 @@
         <v>412</v>
       </c>
       <c r="B143" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C143" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
@@ -4747,10 +4837,10 @@
         <v>420</v>
       </c>
       <c r="B144" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C144" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
@@ -4758,10 +4848,10 @@
         <v>421</v>
       </c>
       <c r="B145" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C145" t="s">
-        <v>295</v>
+        <v>344</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
@@ -4769,10 +4859,10 @@
         <v>427</v>
       </c>
       <c r="B146" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C146" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
@@ -4780,10 +4870,10 @@
         <v>429</v>
       </c>
       <c r="B147" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C147" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
@@ -4791,10 +4881,10 @@
         <v>432</v>
       </c>
       <c r="B148" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C148" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
@@ -4802,10 +4892,10 @@
         <v>497</v>
       </c>
       <c r="B149" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C149" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
@@ -4813,10 +4903,10 @@
         <v>498</v>
       </c>
       <c r="B150" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C150" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
@@ -4824,10 +4914,10 @@
         <v>516</v>
       </c>
       <c r="B151" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C151" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
@@ -4835,10 +4925,10 @@
         <v>517</v>
       </c>
       <c r="B152" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C152" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -4846,10 +4936,10 @@
         <v>518</v>
       </c>
       <c r="B153" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C153" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -4857,10 +4947,10 @@
         <v>523</v>
       </c>
       <c r="B154" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C154" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -4868,10 +4958,10 @@
         <v>526</v>
       </c>
       <c r="B155" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C155" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -4879,10 +4969,10 @@
         <v>555</v>
       </c>
       <c r="B156" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C156" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
@@ -4890,10 +4980,10 @@
         <v>711</v>
       </c>
       <c r="B157" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C157" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
@@ -4901,10 +4991,10 @@
         <v>777</v>
       </c>
       <c r="B158" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C158" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
@@ -4912,10 +5002,10 @@
         <v>875</v>
       </c>
       <c r="B159" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C159" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
@@ -4923,10 +5013,10 @@
         <v>876</v>
       </c>
       <c r="B160" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C160" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
@@ -4934,10 +5024,10 @@
         <v>887</v>
       </c>
       <c r="B161" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C161" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
@@ -4945,76 +5035,186 @@
         <v>888</v>
       </c>
       <c r="B162" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C162" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B163" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="C163" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B164" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C164" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B165" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="C165" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B166" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C166" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="B167" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="C167" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168">
-        <v>950</v>
+        <v>910</v>
       </c>
       <c r="B168" t="s">
         <v>323</v>
       </c>
       <c r="C168" t="s">
         <v>324</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>950</v>
+      </c>
+      <c r="B169" t="s">
+        <v>317</v>
+      </c>
+      <c r="C169" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>3147</v>
+      </c>
+      <c r="B170" t="s">
+        <v>349</v>
+      </c>
+      <c r="C170" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>3151</v>
+      </c>
+      <c r="B171" t="s">
+        <v>351</v>
+      </c>
+      <c r="C171" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>3152</v>
+      </c>
+      <c r="B172" t="s">
+        <v>353</v>
+      </c>
+      <c r="C172" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>3153</v>
+      </c>
+      <c r="B173" t="s">
+        <v>355</v>
+      </c>
+      <c r="C173" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>3156</v>
+      </c>
+      <c r="B174" t="s">
+        <v>357</v>
+      </c>
+      <c r="C174" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>3157</v>
+      </c>
+      <c r="B175" t="s">
+        <v>359</v>
+      </c>
+      <c r="C175" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>3159</v>
+      </c>
+      <c r="B176" t="s">
+        <v>361</v>
+      </c>
+      <c r="C176" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>3678</v>
+      </c>
+      <c r="B177" t="s">
+        <v>363</v>
+      </c>
+      <c r="C177" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>3947</v>
+      </c>
+      <c r="B178" t="s">
+        <v>365</v>
+      </c>
+      <c r="C178" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
